--- a/data/output/evaluasi_19.xlsx
+++ b/data/output/evaluasi_19.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1904" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1905" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1903" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1902" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1900" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1903" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1904" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1901" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1971" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1905" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1902" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1906" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,7 +443,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>kabupaten/kota</t>
+          <t>provinsi</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -465,11 +469,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1904</v>
+        <v>19</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bangka Tengah</t>
+          <t>Kepulauan Bangka Belitung</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,44 +482,352 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>86.17761693585787</v>
+        <v>-3.072687656745561</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1904</v>
+        <v>19</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bangka Tengah</t>
+          <t>Kepulauan Bangka Belitung</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.974074740845722</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>-0.1014306637150135</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+      <c r="D4" t="n">
+        <v>-1.681793529159929</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.926897154399629</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.072687656745561</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.681793529159929</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.261344877621897</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.999618448666886</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.547782139165242</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.057695495931777</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.572815135162053</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.339836350405387</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.767950145767624</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -530,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,57 +879,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bangka Selatan</t>
+          <t>Kabupaten Bangka Barat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>207520.7961464829</v>
+        <v>-0.6766458753420399</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q2-25_ril vs implisit_y-on-y_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bangka Selatan</t>
+          <t>Kabupaten Bangka Barat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.3989753615921693</v>
+        <v>0.7770819865341837</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.70978032566221</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.741420440294036</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.8502572471812784</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -632,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,29 +1065,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bangka Barat</t>
+          <t>Kabupaten Bangka Tengah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.578433653313841</v>
+        <v>-0.1790765298264988</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_net_ekspor_q2-25_ril vs sog_q_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-9.986713134534966</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.1143457785604</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.168756318511344</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -706,6 +1186,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2873623608281939</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.96505625341758</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09363217947904462</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>22.39900566009137</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.657175555278986</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1048576370958813</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -743,6 +1483,80 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-10.72157445364949</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1902</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -752,20 +1566,150 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03948907579684279</v>
+        <v>-0.07351999567841296</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8897744665399538</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.1432953197063563</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.712458486166102</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_19.xlsx
+++ b/data/output/evaluasi_19.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
